--- a/TASK2/Scenariji/SC09_PreporukaPlanaTreninga.xlsx
+++ b/TASK2/Scenariji/SC09_PreporukaPlanaTreninga.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Clan unosi fitness ciljeve i parametre, sistem generira personalizirani sedmicni plan treninga.</t>
+          <t>Član unosi fitness ciljeve i parametre, sistem generiše personalizirani sedmični plan treninga.</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Generisanje personaliziranog plana treninga na osnovu ciljeva clana</t>
+          <t>Generisanje personaliziranog plana treninga na osnovu ciljeva člana</t>
         </is>
       </c>
     </row>
@@ -497,14 +497,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Clan je prijavljen na sistem.</t>
+          <t>Član je prijavljen na sistem.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - uspjesan zavrsetak</t>
+          <t>Posljedice - uspješan završetak</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -516,12 +516,12 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - neuspjesan zavrsetak</t>
+          <t>Posljedice - neuspješan završetak</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Plan nije generisan zbog nedostajucih podataka.</t>
+          <t>Plan nije generisan zbog nedostajućih podataka.</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Clan unosi ciljeve i parametre, sistem izracunava BMI i generira plan.</t>
+          <t>Član unosi ciljeve i parametre, sistem izračunava BMI i generiše plan.</t>
         </is>
       </c>
     </row>
@@ -569,10 +569,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Razliciti nivoi intenziteta (pocetnik, srednji, napredni)</t>
-        </is>
-      </c>
-    </row>
+          <t>Razliciti nivoi intenziteta (početnik, srednji, napredni)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -583,7 +584,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -630,7 +631,7 @@
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>6. Izracunavanje BMI na osnovu tezine i visine</t>
+          <t>6. Izračunavanje BMI na osnovu težine i visine</t>
         </is>
       </c>
     </row>
@@ -669,17 +670,18 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Alternativni Tok - Pocetnik (manje od 10 dolazaka)</t>
+          <t>Alternativni Tok - Početnik (manje od 10 dolazaka)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -698,7 +700,7 @@
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>10b. Sistem postavlja intenzitet na pocetnik</t>
+          <t>10b. Sistem postavlja intenzitet na početnik</t>
         </is>
       </c>
     </row>
@@ -709,17 +711,18 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Alternativni Tok - Napredni (vise od 50 dolazaka)</t>
+          <t>Alternativni Tok - Napredni (više od 50 dolazaka)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -731,7 +734,7 @@
     <row r="34">
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>10a. Sistem detektuje vise od 50 dolazaka</t>
+          <t>10a. Sistem detektuje više od 50 dolazaka</t>
         </is>
       </c>
     </row>
